--- a/Luban/Config/Datas/Levels/L15/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L15/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L15 W1/25; N=45; EHP=275.220000; normal:17x22,normal:18x23</t>
+          <t>L15 W1/25; N=45; EHP=661.773901; normal:17x22,normal:18x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L15 W2/25; N=51; EHP=326.607244; normal:17x26,normal:18x25</t>
+          <t>L15 W2/25; N=51; EHP=785.335912; normal:17x26,normal:18x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>3664136,3664673,3664019,3664136,3664673,3664019,3664136,3664673,3664091,3664136,3664673,3664099,3664136,3664673,3664099,3664136,3664673,3664107,3664136,3664673,3664115,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664136,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144</t>
+          <t>3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664673,3664136,3664136,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144,3664144</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L15 W3/25; N=57; EHP=403.832141; air:2x2,air:11x1,air:12x2,air:13x1,air:14x1,normal:17x17,normal:18x18,swarm:84x15</t>
+          <t>L15 W3/25; N=57; EHP=1049.072172; normal:17x17,normal:18x25,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>3666136,3666673,3666019,3666136,3666673,3666019,3666136,3666673,3666091,3666136,3666673,3666091,3666136,3666673,3666099,3666136,3666673,3666107,3666136,3666673,3666107,3666136,3666673,3666115,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666136,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144</t>
+          <t>3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666673,3666136,3666136,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666144,3666136,3666136,3666136,3666136,3666136,3666136,3666136,3666136</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L15 W4/25; N=63; EHP=513.962341; air:2x2,air:11x2,air:12x1,air:13x2,air:14x1,normal:17x19,normal:18x19,swarm:84x17</t>
+          <t>L15 W4/25; N=63; EHP=1339.116055; normal:17x27,normal:18x19,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>3668136,3668673,3668019,3668668,3668136,3668673,3668091,3668668,3668136,3668673,3668091,3668668,3668136,3668673,3668099,3668868,3668136,3668673,3668107,3668868,3668136,3668673,3668107,3668868,3668136,3668673,3668115,3668868,3668136,3668673,3668115,3668988,3668136,3668673,3668988,3668136,3668673,3668988,3668136,3668673,3668136,3668673,3668136,3668673,3668136,3668673,3668136,3668673,3668136,3668673,3668144,3668673,3668144,3668673,3668144,3668673,3668144,3668144,3668144,3668144,3668144,3668144,3668144,3668144,3668144,3668144,3668144,3668144,3668144</t>
+          <t>3668136,3668019,3668019,3668668,3668136,3668091,3668091,3668668,3668136,3668091,3668091,3668668,3668136,3668099,3668099,3668868,3668136,3668107,3668107,3668868,3668136,3668107,3668107,3668868,3668136,3668115,3668115,3668868,3668136,3668115,3668115,3668988,3668136,3668673,3668988,3668136,3668673,3668988,3668136,3668673,3668136,3668673,3668136,3668673,3668136,3668673,3668136,3668673,3668136,3668673,3668144,3668673,3668144,3668673,3668144,3668673,3668144,3668144,3668144,3668144,3668144,3668144,3668144,3668144,3668144,3668144,3668144,3668144,3668144</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L15 W5/25; N=69; EHP=969.535622; air:2x1,air:11x2,air:12x1,air:13x2,air:14x2,normal:17x16,normal:18x16,medium:83x3,swarm:84x19,medium:108x4,medium:123x3</t>
+          <t>L15 W5/25; N=69; EHP=2359.989207; air:2x2,air:11x4,air:12x2,air:13x4,air:14x4,medium:83x3,medium:108x4,medium:123x3,normal:17x16,normal:18x16,swarm:84x11 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>3670136,3670673,3670242,3670019,3670668,3670136,3670673,3670242,3670019,3670668,3670136,3670673,3670466,3670091,3670668,3670136,3670673,3670466,3670091,3670668,3670136,3670673,3670514,3670099,3670868,3670136,3670673,3670514,3670099,3670868,3670136,3670673,3670786,3670107,3670868,3670136,3670673,3670786,3670115,3670988,3670136,3670673,3670786,3670115,3670988,3670136,3670673,3670988,3670136,3670673,3670988,3670136,3670673,3670136,3670673,3670144,3670673,3670144,3670673,3670144,3670673,3670144,3670673,3670144,3670673,3670144,3670673,3670144,3670673,3670144,3670673,3670144,3670144,3670144,3670144</t>
+          <t>3670136,3670019,3670242,3670019,3670668,3670136,3670019,3670242,3670019,3670668,3670136,3670091,3670466,3670091,3670668,3670136,3670091,3670466,3670091,3670668,3670136,3670099,3670514,3670099,3670868,3670136,3670099,3670514,3670099,3670868,3670136,3670107,3670786,3670107,3670868,3670136,3670115,3670786,3670115,3670988,3670136,3670115,3670786,3670115,3670988,3670136,3670673,3670988,3670136,3670673,3670988,3670136,3670673,3670136,3670673,3670144,3670673,3670144,3670673,3670144,3670673,3670144,3670673,3670144,3670673,3670144,3670673,3670144,3670673,3670144,3670673,3670144,3670144,3670144,3670144</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L15 W6/25; N=75; EHP=989.000000; air:2x2,air:11x2,air:12x2,air:13x1,air:14x2,normal:17x13,normal:18x12,fast:30x2,fast:58x2,fast:64x2,medium:83x4,swarm:84x21,fast:98x3,medium:108x3,medium:123x4</t>
+          <t>L15 W6/25; N=75; EHP=2409.073067; air:2x4,air:11x4,air:12x4,air:13x2,air:14x4,fast:30x2,fast:58x2,fast:64x2,fast:98x3,medium:83x4,medium:108x3,medium:123x4,normal:17x13,normal:18x12,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>3672136,3672673,3672242,3672019,3672668,3672136,3672673,3672242,3672019,3672668,3672136,3672673,3672466,3672091,3672668,3672136,3672673,3672466,3672091,3672668,3672136,3672673,3672466,3672099,3672868,3672136,3672673,3672514,3672099,3672868,3672136,3672673,3672514,3672107,3672868,3672136,3672673,3672786,3672107,3672868,3672136,3672673,3672786,3672115,3672988,3672136,3672673,3672115,3672988,3672136,3672673,3672988,3672136,3672673,3672988,3672136,3672673,3672136,3672673,3672144,3672673,3672144,3672673,3672144,3672673,3672144,3672673,3672144,3672673,3672144,3672673,3672144,3672673,3672144,3672673,3672144,3672144,3672144,3672144,3672144,3672144</t>
+          <t>3672136,3672019,3672242,3672019,3672668,3672136,3672019,3672242,3672019,3672668,3672136,3672091,3672466,3672091,3672668,3672136,3672091,3672466,3672091,3672668,3672136,3672099,3672466,3672099,3672868,3672136,3672099,3672514,3672099,3672868,3672136,3672107,3672514,3672107,3672868,3672136,3672107,3672786,3672107,3672868,3672136,3672115,3672786,3672115,3672988,3672136,3672115,3672115,3672988,3672136,3672673,3672988,3672136,3672673,3672988,3672136,3672673,3672136,3672673,3672144,3672673,3672144,3672673,3672144,3672673,3672144,3672673,3672144,3672673,3672144,3672673,3672144,3672673,3672144,3672673,3672144,3672144,3672144,3672144,3672144,3672144</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L15 W7/25; N=81; EHP=1114.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x14,normal:18x14,fast:30x2,fast:58x3,fast:64x2,medium:83x4,swarm:84x22,fast:98x2,medium:108x4,medium:123x4</t>
+          <t>L15 W7/25; N=81; EHP=2714.429810; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x3,fast:64x2,fast:98x2,medium:83x4,medium:108x4,medium:123x4,normal:17x14,normal:18x14,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3674136,3674673,3674242,3674019,3674668,3674136,3674673,3674242,3674019,3674668,3674136,3674673,3674242,3674091,3674668,3674136,3674673,3674466,3674091,3674668,3674136,3674673,3674466,3674099,3674868,3674136,3674673,3674514,3674099,3674868,3674136,3674673,3674514,3674107,3674868,3674136,3674673,3674514,3674107,3674868,3674136,3674673,3674786,3674115,3674868,3674136,3674673,3674786,3674115,3674988,3674136,3674673,3674988,3674136,3674673,3674988,3674136,3674673,3674988,3674136,3674673,3674136,3674673,3674144,3674673,3674144,3674673,3674144,3674673,3674144,3674673,3674144,3674673,3674144,3674673,3674144,3674673,3674144,3674673,3674144,3674673,3674144,3674144,3674144,3674144,3674144,3674144</t>
+          <t>3674136,3674019,3674242,3674019,3674668,3674136,3674019,3674242,3674019,3674668,3674136,3674091,3674242,3674091,3674668,3674136,3674091,3674466,3674091,3674668,3674136,3674099,3674466,3674099,3674868,3674136,3674099,3674514,3674099,3674868,3674136,3674107,3674514,3674107,3674868,3674136,3674107,3674514,3674107,3674868,3674136,3674115,3674786,3674115,3674868,3674136,3674115,3674786,3674115,3674988,3674136,3674673,3674988,3674136,3674673,3674988,3674136,3674673,3674988,3674136,3674673,3674136,3674673,3674144,3674673,3674144,3674673,3674144,3674673,3674144,3674673,3674144,3674673,3674144,3674673,3674144,3674673,3674144,3674673,3674144,3674673,3674144,3674144,3674144,3674144,3674144,3674144</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L15 W8/25; N=87; EHP=1433.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x15,fast:30x3,fast:58x2,fast:64x3,medium:83x4,swarm:84x24,fast:98x2,medium:108x5,medium:123x4</t>
+          <t>L15 W8/25; N=87; EHP=3488.384572; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x2,fast:64x3,fast:98x2,medium:83x4,medium:108x5,medium:123x4,normal:17x15,normal:18x15,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3676136,3676673,3676242,3676019,3676668,3676136,3676673,3676242,3676019,3676668,3676136,3676673,3676242,3676019,3676668,3676136,3676673,3676466,3676091,3676668,3676136,3676673,3676466,3676091,3676668,3676136,3676673,3676466,3676099,3676868,3676136,3676673,3676514,3676099,3676868,3676136,3676673,3676514,3676107,3676868,3676136,3676673,3676786,3676107,3676868,3676136,3676673,3676786,3676115,3676988,3676136,3676673,3676786,3676115,3676988,3676136,3676673,3676988,3676136,3676673,3676988,3676136,3676673,3676136,3676673,3676136,3676673,3676144,3676673,3676144,3676673,3676144,3676673,3676144,3676673,3676144,3676673,3676144,3676673,3676144,3676673,3676144,3676673,3676144,3676673,3676144,3676673,3676144,3676144,3676144,3676144,3676144,3676144</t>
+          <t>3676136,3676019,3676242,3676019,3676668,3676136,3676019,3676242,3676019,3676668,3676136,3676019,3676242,3676019,3676668,3676136,3676091,3676466,3676091,3676668,3676136,3676091,3676466,3676091,3676668,3676136,3676099,3676466,3676099,3676868,3676136,3676099,3676514,3676099,3676868,3676136,3676107,3676514,3676107,3676868,3676136,3676107,3676786,3676107,3676868,3676136,3676115,3676786,3676115,3676988,3676136,3676115,3676786,3676115,3676988,3676136,3676673,3676988,3676136,3676673,3676988,3676136,3676673,3676136,3676673,3676136,3676673,3676144,3676673,3676144,3676673,3676144,3676673,3676144,3676673,3676144,3676673,3676144,3676673,3676144,3676673,3676144,3676673,3676144,3676673,3676144,3676673,3676144,3676144,3676144,3676144,3676144,3676144</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L15 W9/25; N=93; EHP=1829.000000; air:2x3,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x16,normal:18x16,fast:30x3,fast:58x3,fast:64x2,medium:83x5,swarm:84x26,fast:98x3,medium:108x4,medium:123x4</t>
+          <t>L15 W9/25; N=93; EHP=4454.593322; air:2x6,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x3,fast:64x2,fast:98x3,medium:83x5,medium:108x4,medium:123x4,normal:17x16,normal:18x16,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3678136,3678673,3678242,3678019,3678668,3678136,3678673,3678242,3678019,3678668,3678136,3678673,3678466,3678091,3678668,3678136,3678673,3678466,3678091,3678668,3678136,3678673,3678466,3678091,3678868,3678136,3678673,3678514,3678099,3678868,3678136,3678673,3678514,3678099,3678868,3678136,3678673,3678514,3678107,3678868,3678136,3678673,3678786,3678107,3678868,3678136,3678673,3678786,3678107,3678988,3678136,3678673,3678786,3678115,3678988,3678136,3678673,3678115,3678988,3678136,3678673,3678988,3678136,3678673,3678988,3678136,3678673,3678136,3678673,3678136,3678673,3678136,3678673,3678144,3678673,3678144,3678673,3678144,3678673,3678144,3678673,3678144,3678673,3678144,3678673,3678144,3678673,3678144,3678673,3678144,3678673,3678144,3678144,3678144,3678144,3678144,3678144,3678144,3678144</t>
+          <t>3678136,3678019,3678242,3678019,3678668,3678136,3678019,3678242,3678019,3678668,3678136,3678091,3678466,3678091,3678668,3678136,3678091,3678466,3678091,3678668,3678136,3678091,3678466,3678091,3678868,3678136,3678099,3678514,3678099,3678868,3678136,3678099,3678514,3678099,3678868,3678136,3678107,3678514,3678107,3678868,3678136,3678107,3678786,3678107,3678868,3678136,3678107,3678786,3678107,3678988,3678136,3678115,3678786,3678115,3678988,3678136,3678115,3678115,3678988,3678136,3678673,3678988,3678136,3678673,3678988,3678136,3678673,3678136,3678673,3678136,3678673,3678136,3678673,3678144,3678673,3678144,3678673,3678144,3678673,3678144,3678673,3678144,3678673,3678144,3678673,3678144,3678673,3678144,3678673,3678144,3678673,3678144,3678144,3678144,3678144,3678144,3678144,3678144,3678144</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L15 W10/25; N=99; EHP=3374.000000; air:2x2,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x18,normal:18x17,fast:30x2,fast:58x3,fast:64x3,medium:83x4,swarm:84x27,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L15 W10/25; N=99; EHP=8219.739369; air:2x4,air:11x6,air:12x4,air:13x6,air:14x4,fast:30x2,fast:58x3,fast:64x3,fast:98x3,medium:83x4,medium:108x5,medium:123x5,normal:17x18,normal:18x17,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3680136,3680673,3680242,3680019,3680668,3680253,3680136,3680673,3680242,3680019,3680668,3680253,3680136,3680673,3680242,3680091,3680668,3680325,3680136,3680673,3680466,3680091,3680668,3680541,3680136,3680673,3680466,3680091,3680668,3680565,3680136,3680673,3680466,3680099,3680868,3680645,3680136,3680673,3680514,3680099,3680868,3680693,3680136,3680673,3680514,3680099,3680868,3680693,3680136,3680673,3680514,3680107,3680868,3680709,3680136,3680673,3680786,3680107,3680868,3681021,3680136,3680673,3680786,3680115,3680988,3680136,3680673,3680786,3680115,3680988,3680136,3680673,3680115,3680988,3680144,3680673,3680988,3680144,3680673,3680988,3680144,3680673,3680144,3680673,3680144,3680673,3680144,3680673,3680144,3680673,3680144,3680673,3680144,3680673,3680144,3680673,3680144,3680673,3680144,3680673,3680144,3680673,3680673,3680673,3680673</t>
+          <t>3680136,3680019,3680242,3680019,3680668,3680253,3680136,3680019,3680242,3680019,3680668,3680253,3680136,3680091,3680242,3680091,3680668,3680325,3680136,3680091,3680466,3680091,3680668,3680541,3680136,3680091,3680466,3680091,3680668,3680565,3680136,3680099,3680466,3680099,3680868,3680645,3680136,3680099,3680514,3680099,3680868,3680693,3680136,3680099,3680514,3680099,3680868,3680693,3680136,3680107,3680514,3680107,3680868,3680709,3680136,3680107,3680786,3680107,3680868,3681021,3680136,3680115,3680786,3680115,3680988,3680136,3680115,3680786,3680115,3680988,3680136,3680115,3680115,3680988,3680144,3680673,3680988,3680144,3680673,3680988,3680144,3680673,3680144,3680673,3680144,3680673,3680144,3680673,3680144,3680673,3680144,3680673,3680144,3680673,3680144,3680673,3680144,3680673,3680144,3680673,3680144,3680673,3680673,3680673,3680673</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L15 W11/25; N=105; EHP=3442.000000; air:2x2,air:11x3,air:12x3,air:13x2,air:14x3,normal:17x13,normal:18x13,fast:30x3,heavy:31x2,heavy:40x1,fast:58x3,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x1,medium:83x5,swarm:84x29,heavy:86x2,heavy:88x1,fast:98x3,medium:108x5,medium:123x5,heavy:127x1</t>
+          <t>L15 W11/25; N=105; EHP=8375.637182; air:2x4,air:11x6,air:12x6,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x3,heavy:31x2,heavy:40x1,heavy:67x1,heavy:70x1,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x1,medium:83x5,medium:108x5,medium:123x5,normal:17x13,normal:18x13,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3682136,3682673,3682242,3682019,3682668,3682253,3682136,3682673,3682242,3682019,3682668,3682253,3682136,3682673,3682242,3682019,3682668,3682325,3682136,3682673,3682466,3682091,3682668,3682325,3682136,3682673,3682466,3682091,3682668,3682541,3682136,3682673,3682466,3682099,3682668,3682565,3682136,3682673,3682514,3682099,3682868,3682645,3682136,3682673,3682514,3682099,3682868,3682693,3682136,3682673,3682514,3682107,3682868,3682709,3682136,3682673,3682514,3682107,3682868,3683021,3682136,3682673,3682786,3682115,3682868,3683021,3682136,3682673,3682786,3682115,3682988,3682136,3682673,3682786,3682115,3682988,3682136,3682673,3682988,3682144,3682673,3682988,3682144,3682673,3682988,3682144,3682673,3682144,3682673,3682144,3682673,3682144,3682673,3682144,3682673,3682144,3682673,3682144,3682673,3682144,3682673,3682144,3682673,3682144,3682673,3682144,3682673,3682673,3682673,3682673,3682673</t>
+          <t>3682136,3682019,3682242,3682019,3682668,3682253,3682136,3682019,3682242,3682019,3682668,3682253,3682136,3682019,3682242,3682019,3682668,3682325,3682136,3682091,3682466,3682091,3682668,3682325,3682136,3682091,3682466,3682091,3682668,3682541,3682136,3682099,3682466,3682099,3682668,3682565,3682136,3682099,3682514,3682099,3682868,3682645,3682136,3682099,3682514,3682099,3682868,3682693,3682136,3682107,3682514,3682107,3682868,3682709,3682136,3682107,3682514,3682107,3682868,3683021,3682136,3682115,3682786,3682115,3682868,3683021,3682136,3682115,3682786,3682115,3682988,3682136,3682115,3682786,3682115,3682988,3682136,3682673,3682988,3682144,3682673,3682988,3682144,3682673,3682988,3682144,3682673,3682144,3682673,3682144,3682673,3682144,3682673,3682144,3682673,3682144,3682673,3682144,3682673,3682144,3682673,3682144,3682673,3682144,3682673,3682144,3682673,3682673,3682673,3682673,3682673</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L15 W12/25; N=111; EHP=3562.000000; air:2x3,air:11x2,air:12x3,air:13x2,air:14x3,normal:17x14,normal:18x13,fast:30x3,heavy:31x2,heavy:40x2,fast:58x3,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x1,medium:83x6,swarm:84x31,heavy:86x1,heavy:88x1,fast:98x3,medium:108x5,medium:123x5,heavy:127x2</t>
+          <t>L15 W12/25; N=111; EHP=8661.368416; air:2x6,air:11x4,air:12x6,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x4,fast:98x3,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x6,medium:108x5,medium:123x5,normal:17x14,normal:18x13,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3684136,3684673,3684242,3684019,3684668,3684253,3684136,3684673,3684242,3684019,3684668,3684325,3684136,3684673,3684242,3684019,3684668,3684325,3684136,3684673,3684242,3684091,3684668,3684541,3684136,3684673,3684466,3684091,3684668,3684565,3684136,3684673,3684466,3684091,3684868,3684565,3684136,3684673,3684466,3684099,3684868,3684645,3684136,3684673,3684514,3684099,3684868,3684693,3684136,3684673,3684514,3684099,3684868,3684709,3684136,3684673,3684514,3684107,3684868,3685021,3684136,3684673,3684786,3684107,3684868,3685021,3684136,3684673,3684786,3684107,3684988,3684136,3684673,3684786,3684115,3684988,3684136,3684673,3684786,3684115,3684988,3684144,3684673,3684988,3684144,3684673,3684988,3684144,3684673,3684988,3684144,3684673,3684144,3684673,3684144,3684673,3684144,3684673,3684144,3684673,3684144,3684673,3684144,3684673,3684144,3684673,3684144,3684673,3684144,3684673,3684144,3684673,3684144,3684673,3684673,3684673,3684673</t>
+          <t>3684136,3684019,3684242,3684019,3684668,3684253,3684136,3684019,3684242,3684019,3684668,3684325,3684136,3684019,3684242,3684019,3684668,3684325,3684136,3684091,3684242,3684091,3684668,3684541,3684136,3684091,3684466,3684091,3684668,3684565,3684136,3684091,3684466,3684091,3684868,3684565,3684136,3684099,3684466,3684099,3684868,3684645,3684136,3684099,3684514,3684099,3684868,3684693,3684136,3684099,3684514,3684099,3684868,3684709,3684136,3684107,3684514,3684107,3684868,3685021,3684136,3684107,3684786,3684107,3684868,3685021,3684136,3684107,3684786,3684107,3684988,3684136,3684115,3684786,3684115,3684988,3684136,3684115,3684786,3684115,3684988,3684144,3684673,3684988,3684144,3684673,3684988,3684144,3684673,3684988,3684144,3684673,3684144,3684673,3684144,3684673,3684144,3684673,3684144,3684673,3684144,3684673,3684144,3684673,3684144,3684673,3684144,3684673,3684144,3684673,3684144,3684673,3684144,3684673,3684673,3684673,3684673</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L15 W13/25; N=117; EHP=4346.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x2,normal:17x14,normal:18x15,fast:30x4,heavy:31x1,heavy:40x2,fast:58x3,fast:64x3,heavy:67x1,heavy:70x2,heavy:80x1,medium:83x5,swarm:84x32,heavy:86x1,heavy:88x1,fast:98x4,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L15 W13/25; N=117; EHP=10570.884129; air:2x6,air:11x6,air:12x6,air:13x6,air:14x4,fast:30x4,fast:58x3,fast:64x3,fast:98x4,heavy:31x1,heavy:40x2,heavy:67x1,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x5,medium:108x6,medium:123x6,normal:17x14,normal:18x15,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3686136,3686673,3686242,3686019,3686668,3686253,3686136,3686673,3686242,3686019,3686668,3686325,3686136,3686673,3686242,3686019,3686668,3686541,3686136,3686673,3686466,3686091,3686668,3686541,3686136,3686673,3686466,3686091,3686668,3686565,3686136,3686673,3686466,3686091,3686668,3686565,3686136,3686673,3686466,3686099,3686868,3686645,3686136,3686673,3686514,3686099,3686868,3686693,3686136,3686673,3686514,3686099,3686868,3686709,3686136,3686673,3686514,3686107,3686868,3686709,3686136,3686673,3686786,3686107,3686868,3687021,3686136,3686673,3686786,3686107,3686868,3687021,3686136,3686673,3686786,3686115,3686988,3686136,3686673,3686786,3686115,3686988,3686136,3686673,3686115,3686988,3686144,3686673,3686988,3686144,3686673,3686988,3686144,3686673,3686988,3686144,3686673,3686144,3686673,3686144,3686673,3686144,3686673,3686144,3686673,3686144,3686673,3686144,3686673,3686144,3686673,3686144,3686673,3686144,3686673,3686144,3686673,3686144,3686673,3686673,3686673,3686673,3686673</t>
+          <t>3686136,3686019,3686242,3686019,3686668,3686253,3686136,3686019,3686242,3686019,3686668,3686325,3686136,3686019,3686242,3686019,3686668,3686541,3686136,3686091,3686466,3686091,3686668,3686541,3686136,3686091,3686466,3686091,3686668,3686565,3686136,3686091,3686466,3686091,3686668,3686565,3686136,3686099,3686466,3686099,3686868,3686645,3686136,3686099,3686514,3686099,3686868,3686693,3686136,3686099,3686514,3686099,3686868,3686709,3686136,3686107,3686514,3686107,3686868,3686709,3686136,3686107,3686786,3686107,3686868,3687021,3686136,3686107,3686786,3686107,3686868,3687021,3686136,3686115,3686786,3686115,3686988,3686136,3686115,3686786,3686115,3686988,3686136,3686115,3686115,3686988,3686144,3686673,3686988,3686144,3686673,3686988,3686144,3686673,3686988,3686144,3686673,3686144,3686673,3686144,3686673,3686144,3686673,3686144,3686673,3686144,3686673,3686144,3686673,3686144,3686673,3686144,3686673,3686144,3686673,3686144,3686673,3686144,3686673,3686673,3686673,3686673,3686673</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L15 W14/25; N=123; EHP=5243.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x15,fast:30x3,heavy:31x1,heavy:40x1,fast:58x4,fast:64x3,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x34,heavy:86x1,heavy:88x2,fast:98x4,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L15 W14/25; N=123; EHP=12754.961308; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x3,fast:58x4,fast:64x3,fast:98x4,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3688136,3688673,3688242,3688019,3688668,3688253,3688542,3688136,3688673,3688242,3688019,3688668,3688325,3688136,3688673,3688242,3688019,3688668,3688541,3688136,3688673,3688242,3688091,3688668,3688541,3688136,3688673,3688466,3688091,3688668,3688565,3688136,3688673,3688466,3688091,3688668,3688565,3688136,3688673,3688466,3688099,3688668,3688645,3688136,3688673,3688466,3688099,3688868,3688645,3688136,3688673,3688514,3688099,3688868,3688693,3688136,3688673,3688514,3688107,3688868,3688709,3688136,3688673,3688514,3688107,3688868,3688709,3688136,3688673,3688514,3688107,3688868,3689021,3688136,3688673,3688786,3688115,3688868,3688136,3688673,3688786,3688115,3688988,3688136,3688673,3688786,3688115,3688988,3688144,3688673,3688988,3688144,3688673,3688988,3688144,3688673,3688988,3688144,3688673,3688988,3688144,3688673,3688144,3688673,3688144,3688673,3688144,3688673,3688144,3688673,3688144,3688673,3688144,3688673,3688144,3688673,3688144,3688673,3688144,3688673,3688144,3688673,3688144,3688673,3688673,3688673,3688673,3688673,3688673</t>
+          <t>3688136,3688019,3688242,3688019,3688668,3688253,3688542,3688136,3688019,3688242,3688019,3688668,3688325,3688136,3688019,3688242,3688019,3688668,3688541,3688136,3688091,3688242,3688091,3688668,3688541,3688136,3688091,3688466,3688091,3688668,3688565,3688136,3688091,3688466,3688091,3688668,3688565,3688136,3688099,3688466,3688099,3688668,3688645,3688136,3688099,3688466,3688099,3688868,3688645,3688136,3688099,3688514,3688099,3688868,3688693,3688136,3688107,3688514,3688107,3688868,3688709,3688136,3688107,3688514,3688107,3688868,3688709,3688136,3688107,3688514,3688107,3688868,3689021,3688136,3688115,3688786,3688115,3688868,3688136,3688115,3688786,3688115,3688988,3688136,3688115,3688786,3688115,3688988,3688144,3688673,3688988,3688144,3688673,3688988,3688144,3688673,3688988,3688144,3688673,3688988,3688144,3688673,3688144,3688673,3688144,3688673,3688144,3688673,3688144,3688673,3688144,3688673,3688144,3688673,3688144,3688673,3688144,3688673,3688144,3688673,3688144,3688673,3688144,3688673,3688673,3688673,3688673,3688673,3688673</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L15 W15/25; N=129; EHP=9151.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x16,fast:30x4,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x36,heavy:86x1,heavy:88x2,fast:98x3,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L15 W15/25; N=129; EHP=22244.042349; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,elite:67x1,fast:30x4,fast:58x4,fast:64x4,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x1,medium:83x7,medium:108x6,medium:123x6,normal:17x15,normal:18x16,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3690136,3690673,3690242,3690019,3690668,3690253,3690136,3690673,3690242,3690019,3690668,3690253,3690136,3690673,3690242,3690019,3690668,3690325,3690136,3690673,3690242,3690091,3690668,3690541,3690136,3690673,3690466,3690091,3690668,3690541,3690136,3690673,3690466,3690091,3690668,3690565,3690136,3690673,3690466,3690091,3690868,3690645,3690136,3690673,3690466,3690099,3690868,3690645,3690136,3690673,3690514,3690099,3690868,3690693,3690136,3690673,3690514,3690099,3690868,3690693,3690136,3690673,3690514,3690107,3690868,3690709,3690136,3690673,3690514,3690107,3690868,3690709,3690136,3690673,3690786,3690107,3690868,3691021,3690136,3690673,3690786,3690115,3690988,3690136,3690673,3690786,3690115,3690988,3690136,3690673,3690786,3690115,3690988,3690136,3690673,3690988,3690144,3690673,3690988,3690144,3690673,3690988,3690144,3690673,3690988,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690673,3690673,3690673,3690673</t>
+          <t>3690136,3690019,3690242,3690019,3690668,3690253,3690136,3690019,3690242,3690019,3690668,3690253,3690136,3690019,3690242,3690019,3690668,3690325,3690136,3690091,3690242,3690091,3690668,3690541,3690136,3690091,3690466,3690091,3690668,3690541,3690136,3690091,3690466,3690091,3690668,3690565,3690136,3690091,3690466,3690091,3690868,3690645,3690136,3690099,3690466,3690099,3690868,3690645,3690136,3690099,3690514,3690099,3690868,3690693,3690136,3690099,3690514,3690099,3690868,3690693,3690136,3690107,3690514,3690107,3690868,3690709,3690136,3690107,3690514,3690107,3690868,3690709,3690136,3690107,3690786,3690107,3690868,3691021,3690136,3690115,3690786,3690115,3690988,3690136,3690115,3690786,3690115,3690988,3690136,3690115,3690786,3690115,3690988,3690136,3690673,3690988,3690144,3690673,3690988,3690144,3690673,3690988,3690144,3690673,3690988,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690144,3690673,3690673,3690673,3690673,3690673</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L15 W16/25; N=135; EHP=9335.000000; air:2x3,air:11x4,air:12x3,air:13x3,air:14x3,normal:17x17,normal:18x16,fast:30x4,heavy:31x2,heavy:40x1,fast:58x4,fast:64x4,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x37,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x1</t>
+          <t>L15 W16/25; N=135; EHP=22701.965621; air:2x6,air:11x8,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x1,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x6,medium:108x7,medium:123x7,normal:17x17,normal:18x16,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3692136,3692673,3692242,3692019,3692668,3692253,3692136,3692673,3692242,3692019,3692668,3692253,3692136,3692673,3692242,3692019,3692668,3692325,3692136,3692673,3692242,3692091,3692668,3692325,3692136,3692673,3692466,3692091,3692668,3692541,3692136,3692673,3692466,3692091,3692668,3692565,3692136,3692673,3692466,3692099,3692668,3692645,3692136,3692673,3692466,3692099,3692868,3692645,3692136,3692673,3692514,3692099,3692868,3692693,3692136,3692673,3692514,3692099,3692868,3692693,3692136,3692673,3692514,3692107,3692868,3692709,3692136,3692673,3692514,3692107,3692868,3692709,3692136,3692673,3692786,3692107,3692868,3693021,3692136,3692673,3692786,3692115,3692868,3693021,3692136,3692673,3692786,3692115,3692988,3692136,3692673,3692786,3692115,3692988,3692136,3692673,3692115,3692988,3692144,3692673,3692988,3692144,3692673,3692988,3692144,3692673,3692988,3692144,3692673,3692988,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692673,3692673,3692673,3692673,3692673</t>
+          <t>3692136,3692019,3692242,3692019,3692668,3692253,3692136,3692019,3692242,3692019,3692668,3692253,3692136,3692019,3692242,3692019,3692668,3692325,3692136,3692091,3692242,3692091,3692668,3692325,3692136,3692091,3692466,3692091,3692668,3692541,3692136,3692091,3692466,3692091,3692668,3692565,3692136,3692099,3692466,3692099,3692668,3692645,3692136,3692099,3692466,3692099,3692868,3692645,3692136,3692099,3692514,3692099,3692868,3692693,3692136,3692099,3692514,3692099,3692868,3692693,3692136,3692107,3692514,3692107,3692868,3692709,3692136,3692107,3692514,3692107,3692868,3692709,3692136,3692107,3692786,3692107,3692868,3693021,3692136,3692115,3692786,3692115,3692868,3693021,3692136,3692115,3692786,3692115,3692988,3692136,3692115,3692786,3692115,3692988,3692136,3692115,3692115,3692988,3692144,3692673,3692988,3692144,3692673,3692988,3692144,3692673,3692988,3692144,3692673,3692988,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692144,3692673,3692673,3692673,3692673,3692673,3692673</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L15 W17/25; N=141; EHP=9522.000000; air:2x3,air:11x3,air:12x4,air:13x3,air:14x4,normal:17x17,normal:18x17,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x7,swarm:84x39,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L15 W17/25; N=141; EHP=23160.507976; air:2x6,air:11x6,air:12x8,air:13x6,air:14x8,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x17,normal:18x17,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3694136,3694673,3694242,3694019,3694668,3694253,3694136,3694673,3694242,3694019,3694668,3694253,3694136,3694673,3694242,3694019,3694668,3694325,3694136,3694673,3694242,3694019,3694668,3694325,3694136,3694673,3694466,3694091,3694668,3694541,3694136,3694673,3694466,3694091,3694668,3694565,3694136,3694673,3694466,3694091,3694668,3694565,3694136,3694673,3694466,3694099,3694668,3694645,3694136,3694673,3694514,3694099,3694868,3694645,3694136,3694673,3694514,3694099,3694868,3694693,3694136,3694673,3694514,3694099,3694868,3694693,3694136,3694673,3694514,3694107,3694868,3694709,3694136,3694673,3694786,3694107,3694868,3695021,3694136,3694673,3694786,3694107,3694868,3695021,3694136,3694673,3694786,3694107,3694868,3694136,3694673,3694786,3694115,3694988,3694136,3694673,3694786,3694115,3694988,3694136,3694673,3694115,3694988,3694144,3694673,3694988,3694144,3694673,3694988,3694144,3694673,3694988,3694144,3694673,3694988,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694673,3694673,3694673,3694673,3694673,3694673</t>
+          <t>3694136,3694019,3694242,3694019,3694668,3694253,3694136,3694019,3694242,3694019,3694668,3694253,3694136,3694019,3694242,3694019,3694668,3694325,3694136,3694019,3694242,3694019,3694668,3694325,3694136,3694091,3694466,3694091,3694668,3694541,3694136,3694091,3694466,3694091,3694668,3694565,3694136,3694091,3694466,3694091,3694668,3694565,3694136,3694099,3694466,3694099,3694668,3694645,3694136,3694099,3694514,3694099,3694868,3694645,3694136,3694099,3694514,3694099,3694868,3694693,3694136,3694099,3694514,3694099,3694868,3694693,3694136,3694107,3694514,3694107,3694868,3694709,3694136,3694107,3694786,3694107,3694868,3695021,3694136,3694107,3694786,3694107,3694868,3695021,3694136,3694107,3694786,3694107,3694868,3694136,3694115,3694786,3694115,3694988,3694136,3694115,3694786,3694115,3694988,3694136,3694115,3694115,3694988,3694144,3694673,3694988,3694144,3694673,3694988,3694144,3694673,3694988,3694144,3694673,3694988,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694144,3694673,3694673,3694673,3694673,3694673,3694673,3694673</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L15 W18/25; N=147; EHP=10174.000000; air:2x4,air:11x3,air:12x4,air:13x4,air:14x3,normal:17x18,normal:18x17,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x41,heavy:86x2,heavy:88x1,fast:98x5,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L15 W18/25; N=147; EHP=24752.597785; air:2x8,air:11x6,air:12x8,air:13x8,air:14x6,fast:30x4,fast:58x4,fast:64x4,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x8,medium:108x7,medium:123x7,normal:17x18,normal:18x17,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3696136,3696673,3696242,3696019,3696668,3696253,3696136,3696673,3696242,3696019,3696668,3696253,3696136,3696673,3696242,3696019,3696668,3696325,3696136,3696673,3696242,3696019,3696668,3696325,3696136,3696673,3696466,3696091,3696668,3696541,3696136,3696673,3696466,3696091,3696668,3696541,3696136,3696673,3696466,3696091,3696668,3696565,3696136,3696673,3696466,3696091,3696868,3696565,3696136,3696673,3696466,3696099,3696868,3696645,3696136,3696673,3696514,3696099,3696868,3696693,3696136,3696673,3696514,3696099,3696868,3696693,3696136,3696673,3696514,3696107,3696868,3696709,3696136,3696673,3696514,3696107,3696868,3696709,3696136,3696673,3696514,3696107,3696868,3697021,3696136,3696673,3696786,3696107,3696988,3697021,3696136,3696673,3696786,3696115,3696988,3696136,3696673,3696786,3696115,3696988,3696136,3696673,3696786,3696115,3696988,3696136,3696673,3696988,3696144,3696673,3696988,3696144,3696673,3696988,3696144,3696673,3696988,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696673,3696673,3696673,3696673</t>
+          <t>3696136,3696019,3696242,3696019,3696668,3696253,3696136,3696019,3696242,3696019,3696668,3696253,3696136,3696019,3696242,3696019,3696668,3696325,3696136,3696019,3696242,3696019,3696668,3696325,3696136,3696091,3696466,3696091,3696668,3696541,3696136,3696091,3696466,3696091,3696668,3696541,3696136,3696091,3696466,3696091,3696668,3696565,3696136,3696091,3696466,3696091,3696868,3696565,3696136,3696099,3696466,3696099,3696868,3696645,3696136,3696099,3696514,3696099,3696868,3696693,3696136,3696099,3696514,3696099,3696868,3696693,3696136,3696107,3696514,3696107,3696868,3696709,3696136,3696107,3696514,3696107,3696868,3696709,3696136,3696107,3696514,3696107,3696868,3697021,3696136,3696107,3696786,3696107,3696988,3697021,3696136,3696115,3696786,3696115,3696988,3696136,3696115,3696786,3696115,3696988,3696136,3696115,3696786,3696115,3696988,3696136,3696673,3696988,3696144,3696673,3696988,3696144,3696673,3696988,3696144,3696673,3696988,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696144,3696673,3696673,3696673,3696673,3696673</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L15 W19/25; N=153; EHP=11784.000000; air:2x4,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x19,normal:18x19,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x7,swarm:84x42,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x8,heavy:127x2</t>
+          <t>L15 W19/25; N=153; EHP=28655.516656; air:2x8,air:11x8,air:12x6,air:13x8,air:14x6,fast:30x4,fast:58x5,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x8,normal:17x19,normal:18x19,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3698136,3698673,3698242,3698019,3698668,3698253,3698542,3698136,3698673,3698242,3698019,3698668,3698253,3698136,3698673,3698242,3698019,3698668,3698325,3698136,3698673,3698242,3698091,3698668,3698325,3698136,3698673,3698242,3698091,3698668,3698541,3698136,3698673,3698466,3698091,3698668,3698541,3698136,3698673,3698466,3698091,3698668,3698565,3698136,3698673,3698466,3698099,3698668,3698565,3698136,3698673,3698466,3698099,3698868,3698645,3698136,3698673,3698514,3698099,3698868,3698645,3698136,3698673,3698514,3698099,3698868,3698693,3698136,3698673,3698514,3698107,3698868,3698709,3698136,3698673,3698514,3698107,3698868,3698709,3698136,3698673,3698514,3698107,3698868,3699021,3698136,3698673,3698786,3698107,3698868,3699021,3698136,3698673,3698786,3698115,3698868,3698136,3698673,3698786,3698115,3698988,3698136,3698673,3698786,3698115,3698988,3698136,3698673,3698786,3698115,3698988,3698144,3698673,3698988,3698144,3698673,3698988,3698144,3698673,3698988,3698144,3698673,3698988,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698673,3698673,3698673,3698673,3698673,3698673</t>
+          <t>3698136,3698019,3698242,3698019,3698668,3698253,3698542,3698136,3698019,3698242,3698019,3698668,3698253,3698136,3698019,3698242,3698019,3698668,3698325,3698136,3698091,3698242,3698091,3698668,3698325,3698136,3698091,3698242,3698091,3698668,3698541,3698136,3698091,3698466,3698091,3698668,3698541,3698136,3698091,3698466,3698091,3698668,3698565,3698136,3698099,3698466,3698099,3698668,3698565,3698136,3698099,3698466,3698099,3698868,3698645,3698136,3698099,3698514,3698099,3698868,3698645,3698136,3698099,3698514,3698099,3698868,3698693,3698136,3698107,3698514,3698107,3698868,3698709,3698136,3698107,3698514,3698107,3698868,3698709,3698136,3698107,3698514,3698107,3698868,3699021,3698136,3698107,3698786,3698107,3698868,3699021,3698136,3698115,3698786,3698115,3698868,3698136,3698115,3698786,3698115,3698988,3698136,3698115,3698786,3698115,3698988,3698136,3698115,3698786,3698115,3698988,3698144,3698673,3698988,3698144,3698673,3698988,3698144,3698673,3698988,3698144,3698673,3698988,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698144,3698673,3698673,3698673,3698673,3698673,3698673,3698673</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L15 W20/25; N=159; EHP=19785.000000; air:2x3,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x19,normal:18x19,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x44,heavy:86x1,heavy:88x2,fast:98x5,medium:108x8,medium:123x7,heavy:127x2</t>
+          <t>L15 W20/25; N=159; EHP=48110.959863; air:2x6,air:11x8,air:12x8,air:13x8,air:14x8,elite:67x1,fast:30x5,fast:58x4,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x7,normal:17x19,normal:18x19,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10017907,10017917,10017909,10048610,10017916,10045186,10017907,10017917,10017909,10048610,10017916,10045186,10017907,10017917,10017909,10048610,10017916,10017910,10017907,10017917,10017909,10048610,10017916,10017910,10017907,10017917,10017909,10017904,10017916,10017913,10017907,10017917,10017911,10017904,10017916,10017913,10017907,10017917,10017911,10017904,10017916,10017914,10017907,10017917,10017911,10017904,10017916,10017914,10017907,10017917,10017911,10048611,10017921,10017915,10017907,10017917,10017911,10048611,10017921,10017915,10017907,10017917,10017912,10048611,10017921,10017918,10017907,10017917,10017912,10048611,10017921,10017918,10017907,10017917,10017912,10017905,10017921,10017919,10017907,10017917,10017912,10017905,10017921,10017919,10017907,10017917,10017920,10017905,10017921,10017923,10017907,10017917,10017920,10017905,10017921,10017923,10017907,10017917,10017920,10017906,10017922,10017907,10017917,10017920,10017906,10017922,10017907,10017917,10017920,10017906,10017922,10017907,10017917,10017906,10017922,10017908,10017917,10017922,10017908,10017917,10017922,10017908,10017917,10017922,10017908,10017917,10017922,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017917,10017917,10017917,10017917,10017917,10017917</t>
+          <t>10017907,10048610,10017909,10048610,10017916,10045186,10017907,10048610,10017909,10048610,10017916,10045186,10017907,10048610,10017909,10048610,10017916,10017910,10017907,10048610,10017909,10048610,10017916,10017910,10017907,10017904,10017909,10017904,10017916,10017913,10017907,10017904,10017911,10017904,10017916,10017913,10017907,10017904,10017911,10017904,10017916,10017914,10017907,10017904,10017911,10017904,10017916,10017914,10017907,10048611,10017911,10048611,10017921,10017915,10017907,10048611,10017911,10048611,10017921,10017915,10017907,10048611,10017912,10048611,10017921,10017918,10017907,10048611,10017912,10048611,10017921,10017918,10017907,10017905,10017912,10017905,10017921,10017919,10017907,10017905,10017912,10017905,10017921,10017919,10017907,10017905,10017920,10017905,10017921,10017923,10017907,10017905,10017920,10017905,10017921,10017923,10017907,10017906,10017920,10017906,10017922,10017907,10017906,10017920,10017906,10017922,10017907,10017906,10017920,10017906,10017922,10017907,10017906,10017906,10017922,10017908,10017917,10017922,10017908,10017917,10017922,10017908,10017917,10017922,10017908,10017917,10017922,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017908,10017917,10017917,10017917,10017917,10017917,10017917,10017917</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L15 W21/25; N=165; EHP=20181.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x46,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L15 W21/25; N=165; EHP=49093.144734; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x4,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x20,normal:18x20,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10017927,10017937,10017929,10048612,10017936,10017930,10017927,10017937,10017929,10048612,10017936,10017930,10017927,10017937,10017929,10048612,10017936,10045187,10017927,10017937,10017929,10048612,10017936,10045187,10017927,10017937,10017929,10017924,10017936,10017933,10017927,10017937,10017931,10017924,10017936,10017933,10017927,10017937,10017931,10017924,10017936,10017934,10017927,10017937,10017931,10017924,10017936,10017934,10017927,10017937,10017931,10048613,10017941,10017935,10017927,10017937,10017931,10048613,10017941,10017935,10017927,10017937,10017932,10048613,10017941,10017938,10017927,10017937,10017932,10048613,10017941,10017938,10017927,10017937,10017932,10017925,10017941,10017939,10017927,10017937,10017932,10017925,10017941,10017939,10017927,10017937,10017932,10017925,10017941,10017943,10017927,10017937,10017940,10017925,10017941,10017943,10017927,10017937,10017940,10017926,10017942,10017943,10017927,10017937,10017940,10017926,10017942,10017927,10017937,10017940,10017926,10017942,10017927,10017937,10017940,10017926,10017942,10017927,10017937,10017926,10017942,10017928,10017937,10017942,10017928,10017937,10017942,10017928,10017937,10017942,10017928,10017937,10017942,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017937,10017937,10017937,10017937,10017937,10017937</t>
+          <t>10017927,10048612,10017929,10048612,10017936,10017930,10017927,10048612,10017929,10048612,10017936,10017930,10017927,10048612,10017929,10048612,10017936,10045187,10017927,10048612,10017929,10048612,10017936,10045187,10017927,10017924,10017929,10017924,10017936,10017933,10017927,10017924,10017931,10017924,10017936,10017933,10017927,10017924,10017931,10017924,10017936,10017934,10017927,10017924,10017931,10017924,10017936,10017934,10017927,10048613,10017931,10048613,10017941,10017935,10017927,10048613,10017931,10048613,10017941,10017935,10017927,10048613,10017932,10048613,10017941,10017938,10017927,10048613,10017932,10048613,10017941,10017938,10017927,10017925,10017932,10017925,10017941,10017939,10017927,10017925,10017932,10017925,10017941,10017939,10017927,10017925,10017932,10017925,10017941,10017943,10017927,10017925,10017940,10017925,10017941,10017943,10017927,10017926,10017940,10017926,10017942,10017943,10017927,10017926,10017940,10017926,10017942,10017927,10017926,10017940,10017926,10017942,10017927,10017926,10017940,10017926,10017942,10017927,10017926,10017926,10017942,10017928,10017937,10017942,10017928,10017937,10017942,10017928,10017937,10017942,10017928,10017937,10017942,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017928,10017937,10017937,10017937,10017937,10017937,10017937,10017937</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L15 W22/25; N=171; EHP=20585.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x5,normal:17x21,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x47,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x9,heavy:127x3</t>
+          <t>L15 W22/25; N=171; EHP=50081.470615; air:2x8,air:11x8,air:12x8,air:13x8,air:14x10,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x8,medium:108x8,medium:123x9,normal:17x21,normal:18x20,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10017947,10017958,10017949,10048614,10017957,10017950,10017947,10017958,10017949,10048614,10017957,10017950,10017947,10017958,10017949,10048614,10017957,10017951,10017947,10017958,10017949,10048614,10017957,10017951,10017947,10017958,10017949,10017944,10017957,10017954,10017947,10017958,10017952,10017944,10017957,10017954,10017947,10017958,10017952,10017944,10017957,10017955,10017947,10017958,10017952,10017944,10017957,10017955,10017947,10017958,10017952,10048615,10017957,10017955,10017947,10017958,10017952,10048615,10017962,10017956,10017947,10017958,10017952,10048615,10017962,10017956,10017947,10017958,10017953,10048615,10017962,10017959,10017947,10017958,10017953,10048615,10017962,10017959,10017947,10017958,10017953,10017945,10017962,10017960,10017947,10017958,10017953,10017945,10017962,10017960,10017947,10017958,10017953,10017945,10017962,10045188,10017947,10017958,10017961,10017945,10017962,10045188,10017947,10017958,10017961,10017946,10017962,10017947,10017958,10017961,10017946,10017963,10017947,10017958,10017961,10017946,10017963,10017947,10017958,10017961,10017946,10017963,10017948,10017958,10017963,10017948,10017958,10017963,10017948,10017958,10017963,10017948,10017958,10017963,10017948,10017958,10017963,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017958,10017958,10017958,10017958,10017958,10017958</t>
+          <t>10017947,10048614,10017949,10048614,10017957,10017950,10017947,10048614,10017949,10048614,10017957,10017950,10017947,10048614,10017949,10048614,10017957,10017951,10017947,10048614,10017949,10048614,10017957,10017951,10017947,10017944,10017949,10017944,10017957,10017954,10017947,10017944,10017952,10017944,10017957,10017954,10017947,10017944,10017952,10017944,10017957,10017955,10017947,10017944,10017952,10017944,10017957,10017955,10017947,10048615,10017952,10048615,10017957,10017955,10017947,10048615,10017952,10048615,10017962,10017956,10017947,10048615,10017952,10048615,10017962,10017956,10017947,10048615,10017953,10048615,10017962,10017959,10017947,10048615,10017953,10048615,10017962,10017959,10017947,10017945,10017953,10017945,10017962,10017960,10017947,10017945,10017953,10017945,10017962,10017960,10017947,10017945,10017953,10017945,10017962,10045188,10017947,10017945,10017961,10017945,10017962,10045188,10017947,10017946,10017961,10017946,10017962,10017947,10017946,10017961,10017946,10017963,10017947,10017946,10017961,10017946,10017963,10017947,10017946,10017961,10017946,10017963,10017948,10017958,10017963,10017948,10017958,10017963,10017948,10017958,10017963,10017948,10017958,10017963,10017948,10017958,10017963,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017948,10017958,10017958,10017958,10017958,10017958,10017958,10017958</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L15 W23/25; N=177; EHP=20997.000000; air:2x4,air:11x4,air:12x5,air:13x4,air:14x4,normal:17x21,normal:18x22,fast:30x5,heavy:31x2,heavy:40x2,fast:58x6,fast:64x5,heavy:67x2,heavy:70x3,heavy:80x2,medium:83x9,swarm:84x49,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x8,heavy:127x2</t>
+          <t>L15 W23/25; N=177; EHP=51064.855907; air:2x8,air:11x8,air:12x10,air:13x8,air:14x8,fast:30x5,fast:58x6,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x8,normal:17x21,normal:18x22,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10017967,10017977,10017969,10048616,10017976,10017970,10017967,10017977,10017969,10048616,10017976,10017970,10017967,10017977,10017969,10048616,10017976,10017971,10017967,10017977,10017969,10048616,10017976,10017971,10017967,10017977,10017969,10048616,10017976,10017974,10017967,10017977,10017972,10017964,10017976,10017974,10017967,10017977,10017972,10017964,10017976,10017974,10017967,10017977,10017972,10017964,10017976,10045189,10017967,10017977,10017972,10017964,10017976,10045189,10017967,10017977,10017972,10048617,10017981,10017975,10017967,10017977,10017973,10048617,10017981,10017975,10017967,10017977,10017973,10048617,10017981,10017978,10017967,10017977,10017973,10048617,10017981,10017978,10017967,10017977,10017973,10017965,10017981,10017979,10017967,10017977,10017973,10017965,10017981,10017979,10017967,10017977,10017973,10017965,10017981,10017979,10017967,10017977,10017980,10017965,10017981,10017983,10017967,10017977,10017980,10017965,10017981,10017983,10017967,10017977,10017980,10017966,10017982,10017967,10017977,10017980,10017966,10017982,10017967,10017977,10017980,10017966,10017982,10017967,10017977,10017966,10017982,10017968,10017977,10017982,10017968,10017977,10017982,10017968,10017977,10017982,10017968,10017977,10017982,10017968,10017977,10017982,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017977,10017977,10017977,10017977,10017977,10017977,10017977</t>
+          <t>10017967,10048616,10017969,10048616,10017976,10017970,10017967,10048616,10017969,10048616,10017976,10017970,10017967,10048616,10017969,10048616,10017976,10017971,10017967,10048616,10017969,10048616,10017976,10017971,10017967,10048616,10017969,10048616,10017976,10017974,10017967,10017964,10017972,10017964,10017976,10017974,10017967,10017964,10017972,10017964,10017976,10017974,10017967,10017964,10017972,10017964,10017976,10045189,10017967,10017964,10017972,10017964,10017976,10045189,10017967,10048617,10017972,10048617,10017981,10017975,10017967,10048617,10017973,10048617,10017981,10017975,10017967,10048617,10017973,10048617,10017981,10017978,10017967,10048617,10017973,10048617,10017981,10017978,10017967,10017965,10017973,10017965,10017981,10017979,10017967,10017965,10017973,10017965,10017981,10017979,10017967,10017965,10017973,10017965,10017981,10017979,10017967,10017965,10017980,10017965,10017981,10017983,10017967,10017965,10017980,10017965,10017981,10017983,10017967,10017966,10017980,10017966,10017982,10017967,10017966,10017980,10017966,10017982,10017967,10017966,10017980,10017966,10017982,10017967,10017966,10017966,10017982,10017968,10017977,10017982,10017968,10017977,10017982,10017968,10017977,10017982,10017968,10017977,10017982,10017968,10017977,10017982,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017968,10017977,10017977,10017977,10017977,10017977,10017977,10017977,10017977</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L15 W24/25; N=183; EHP=22484.000000; air:2x5,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x22,normal:18x22,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x6,heavy:67x3,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x51,heavy:86x2,heavy:88x3,fast:98x5,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L15 W24/25; N=183; EHP=54688.065377; air:2x10,air:11x8,air:12x8,air:13x10,air:14x8,fast:30x5,fast:58x5,fast:64x6,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x3,heavy:127x2,medium:83x9,medium:108x9,medium:123x9,normal:17x22,normal:18x22,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10017987,10017998,10017989,10048618,10017997,10017990,10018005,10017987,10017998,10017989,10048618,10017997,10017990,10017987,10017998,10017989,10048618,10017997,10017991,10017987,10017998,10017989,10048618,10017997,10017991,10017987,10017998,10017989,10017984,10017997,10017994,10017987,10017998,10017989,10017984,10017997,10017994,10017987,10017998,10017992,10017984,10017997,10017995,10017987,10017998,10017992,10017984,10017997,10017995,10017987,10017998,10017992,10017984,10017997,10017996,10017987,10017998,10017992,10048619,10018002,10017996,10017987,10017998,10017992,10048619,10018002,10017996,10017987,10017998,10017993,10048619,10018002,10017999,10017987,10017998,10017993,10048619,10018002,10017999,10017987,10017998,10017993,10017985,10018002,10018000,10017987,10017998,10017993,10017985,10018002,10018000,10017987,10017998,10017993,10017985,10018002,10018000,10017987,10017998,10018001,10017985,10018002,10018004,10017987,10017998,10018001,10017985,10018002,10018004,10017987,10017998,10018001,10017986,10018003,10017987,10017998,10018001,10017986,10018003,10017987,10017998,10018001,10017986,10018003,10017987,10017998,10018001,10017986,10018003,10017988,10017998,10017986,10018003,10017988,10017998,10018003,10017988,10017998,10018003,10017988,10017998,10018003,10017988,10017998,10018003,10017988,10017998,10018003,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017998,10017998,10017998,10017998,10017998,10017998,10017998</t>
+          <t>10017987,10048618,10017989,10048618,10017997,10017990,10018005,10017987,10048618,10017989,10048618,10017997,10017990,10017987,10048618,10017989,10048618,10017997,10017991,10017987,10048618,10017989,10048618,10017997,10017991,10017987,10017984,10017989,10017984,10017997,10017994,10017987,10017984,10017989,10017984,10017997,10017994,10017987,10017984,10017992,10017984,10017997,10017995,10017987,10017984,10017992,10017984,10017997,10017995,10017987,10017984,10017992,10017984,10017997,10017996,10017987,10048619,10017992,10048619,10018002,10017996,10017987,10048619,10017992,10048619,10018002,10017996,10017987,10048619,10017993,10048619,10018002,10017999,10017987,10048619,10017993,10048619,10018002,10017999,10017987,10017985,10017993,10017985,10018002,10018000,10017987,10017985,10017993,10017985,10018002,10018000,10017987,10017985,10017993,10017985,10018002,10018000,10017987,10017985,10018001,10017985,10018002,10018004,10017987,10017985,10018001,10017985,10018002,10018004,10017987,10017986,10018001,10017986,10018003,10017987,10017986,10018001,10017986,10018003,10017987,10017986,10018001,10017986,10018003,10017987,10017986,10018001,10017986,10018003,10017988,10017986,10017986,10018003,10017988,10017998,10018003,10017988,10017998,10018003,10017988,10017998,10018003,10017988,10017998,10018003,10017988,10017998,10018003,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017988,10017998,10017998,10017998,10017998,10017998,10017998,10017998,10017998</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L15 W25/25; N=189; EHP=44877.000000; air:2x4,air:11x5,air:12x4,air:13x5,air:14x5,normal:17x22,normal:18x23,fast:30x6,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x3,medium:83x9,swarm:84x52,heavy:86x2,heavy:88x3,fast:98x6,medium:108x9,medium:123x10,heavy:127x2,boss:132x1</t>
+          <t>L15 W25/25; N=189; EHP=109148.586224; air:2x8,air:11x10,air:12x8,air:13x10,air:14x10,boss:132x1,fast:30x6,fast:58x5,fast:64x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x3,heavy:86x2,heavy:88x3,heavy:127x2,medium:83x9,medium:108x9,medium:123x10,normal:17x22,normal:18x23,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L15/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L15/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>252</v>
+        <v>330</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>245</v>
+        <v>300</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>231</v>
+        <v>350</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>224</v>
+        <v>190</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>217</v>
+        <v>280</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>203</v>
+        <v>350</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>196</v>
+        <v>280</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>182</v>
+        <v>290</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>175</v>
+        <v>270</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>168</v>
+        <v>350</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>161</v>
+        <v>270</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>154</v>
+        <v>220</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>147</v>
+        <v>290</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>133</v>
+        <v>350</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>128</v>
+        <v>270</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>210</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>270</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>250</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>350</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>195</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
